--- a/uploads/KQCO2003.xlsx
+++ b/uploads/KQCO2003.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\longtruong2604\vscode-projects\datn\flask-test\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EF2EFB1-74AA-46D5-9C00-FE75BD3F6B9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36799F13-63A7-47DB-B4D0-F8F092CAD83A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{CFE92A96-9DAA-461E-ACEF-6E68D901E221}"/>
   </bookViews>
